--- a/docs/REPAIR01_20260823/03 · الدستور.xlsx
+++ b/docs/REPAIR01_20260823/03 · الدستور.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F_تتبع_الحقول_والقواميس" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="G_رحلات_E2E" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H_الاختبار_والقبول" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="J_خريطة_المصادر_الحاكمة" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -676,7 +677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -760,7 +761,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>17 إدارة معتمدة + مساحة عملي + المراجعة الداخلية (خارج التعداد) = 19 وحدة مبنية · 395 شاشة · 6910 حقلًا · والقيادة بملفها المستقل</t>
+          <t>17 إدارة معتمدة + مساحة عملي + المراجعة الداخلية (خارج التعداد) = 19 وحدة مبنية · 396 شاشة · 6931 حقلًا · والقيادة بملفها المستقل</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -834,12 +835,12 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>م 111</t>
+          <t>م 115</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>الصفر المقيس يُكتب صفرًا ولا يُترك فراغًا: الفراغ يعني «غير مقيس» والصفر يعني «قيس فكان صفرًا» — وكل أداة توليد تُفحص بأن تُخرِج صفرًا واحدًا مقيسًا وتُقرأ صفرًا لا خانةً خالية</t>
+          <t>الحقيقة الحاكمة تتحرك في اتجاه واحد: مصدرٌ حاكم ← هدف ← تنفيذ ← زمنُ تشغيل ← دليل. ويُمنع العكس — أن يُشتقّ الهدف من الوضع القائم ثم يُقاس الوضع بنفسه. وما اشتُقّ من الحاضر يُسمّى لقطةَ حالةٍ راهنة ولا يصير هدفًا حاكمًا إلا بحكمٍ مستقل</t>
         </is>
       </c>
       <c r="C11" s="2" t="n"/>
@@ -850,12 +851,12 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>م 112</t>
+          <t>م 116</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>كل حقل في سجل الحقول يحمل مصدره: الجدول أو الكيان الذي جاء منه إلى جانب اسمه التقني — وبلا مفتاح المصدر لا تُربط سياسة على مستوى الحقل (حساسية · تقنيع · صلاحية) إلا بالاسم وحده وهو يُفرِط في الوسم عبر الشاشات</t>
+          <t>كل سجلٍّ يُعلَن حاكمًا يجب أن يجيب أربعة: من يكتبه · ومن يقرؤه في زمن التشغيل · وأين يُنفَّذ حكمه · وكيف يُكتشف انحرافه عن الواقع. وما لا قارئ إنتاجٍ له يُوصَل بالإنتاج أو يُخفَّض إلى مرجعٍ وتوثيق — ولا يبقى حاكمًا بالاسم</t>
         </is>
       </c>
       <c r="C12" s="2" t="n"/>
@@ -866,12 +867,12 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>م 101</t>
+          <t>م 117</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>كل سطح يُسجَّل مصدرَ حقيقة يحمل صراحةً أربعًا: الحبّة · والإدارة المالكة · والكيان المعياري · والمعرّف المعياري — وبوابة تكشف سطحين مصدرَي حقيقة لكيان وحبّة واحدة وتمنع إنشاء حالة جديدة</t>
+          <t>الحقيقة السياقية لا تُخزَّن علاقةً عالمية: ما يعتمد على المساحة أو الإدارة أو الكيان أو المشروع أو العقد أو الدور أو الإصدار أو الزمن لا يُختزل إلى علاقةٍ واحدةٍ لواحد إن كانت حقيقته واحدًا لمتعدد — ويُفحص ذلك في المفاتيح والقيود الفريدة الحاكمة</t>
         </is>
       </c>
       <c r="C13" s="2" t="n"/>
@@ -882,12 +883,12 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>م 102</t>
+          <t>م 118</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>التقرير الذي يجمع أكثر من إدارة لا يملك الحقائق التي يجمعها — يُصنَّف إسقاطًا مؤسسيًّا مشتركًا وتبقى كل حقيقة عند مالكها ولا يُجبَر على مالك واحد منها</t>
+          <t>لا سقوط صامت إلى مسارٍ قديم: إن تعذّر الحكم الجديد فالبديل معلَنٌ ومسجَّلٌ ومحدَّد النطاق ومؤقتٌ إن كان انتقاليًّا وقابلٌ للقياس — والفشل الذي يُنتج نتيجةً تبدو معقولةً وهي مخالفة أخطر من الفشل الظاهر</t>
         </is>
       </c>
       <c r="C14" s="2" t="n"/>
@@ -898,12 +899,12 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>م 103</t>
+          <t>م 119</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>السطح الذي تحتاجه كل الإدارات يُبنى إسقاطًا موحّدًا معلَّمًا بنطاق الإدارة والدور والمشروع — لا نسخة لكل إدارة</t>
+          <t>كل مقياسٍ يحمل ثمانيًا: السؤال الذي يجيب عنه · والبسط · والمقام · والاستبعادات وأسبابها · ومصدر البيانات · ومعرّف اللقطة · واتجاه التحسّن · ومعيار النجاح. ولا مئةٌ بالمئة بمقامٍ مخفيّ، ولا أخضرُ يجيب سؤالًا غير المطلوب</t>
         </is>
       </c>
       <c r="C15" s="2" t="n"/>
@@ -914,12 +915,12 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>م 104</t>
+          <t>م 120</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>لا يُدمج سطح تبويبًا إلا بإثبات الأب المعياري وحبّة الابن ونوع العلاقة ودورة حياته وصلاحيته المستقلة ورابطه العميق وحاجته للوصول المباشر — ولا تُضحّى الصلاحية لأجل ترتيب أجمل للسايدبار</t>
+          <t>حالات الإغلاق ستٌّ مستقلة لا تُقفَز بينها: محسوم ← مبنيّ ← موصول ← مُمارَس ← مُثبَت ← مغلقٌ بالدليل. وموصولٌ لا يساوي مُثبَتًا · ومبنيٌّ لا يساوي فاعلًا في زمن التشغيل · وصحةُ السجل لا تساوي صحةَ الواجهة</t>
         </is>
       </c>
       <c r="C16" s="2" t="n"/>
@@ -930,12 +931,12 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>م 105</t>
+          <t>م 121</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>معيار إغلاق النقص تغطية المؤهَّل لا العدد: مكوّن مركزي واحد يُستدعى في الأسطح المؤهَّلة، ولا يُوضع على استمارة فردية ولا لوحة ولا إعداد ثابت لبلوغ رقم</t>
+          <t>نسب الهدف لا ينقطع عند البناء: لكل هدفٍ معرّفٌ ثابت منذ تعريفه في مصدره الحاكم، وعند بنائه يرتبط معرّف الشاشة بالهدف نفسه — ولا يُستبدل الهدف باسمٍ جديد ولا بمعرّفٍ منفصلٍ بلا نسب</t>
         </is>
       </c>
       <c r="C17" s="2" t="n"/>
@@ -946,12 +947,12 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>م 106</t>
+          <t>م 122</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>يمنع تشغيل المصالحة ثلاثة: تكرار مصدر الحقيقة · وسطح يكتب ومالك حقيقته مجهول · ومسار كتابة يعبر حدود إدارة بلا عقد معتمد — ولا يمنعها السطح القارئ اليتيم؛ يُعلَن استثناءً ويُستثنى من المقام المغلق</t>
+          <t>لكل كونٍ مصدرٌ حاكم مُعلَن في خريطة المصادر: الإدارات السبع عشرة بأوراق الدليل المعماري · ومساحتا الرئيس والنواب بملف القيادة · ومساحة عملي بمواصفتها · والمراجعة الداخلية بمعماريتها · والقدرات المنصّية بأحكامها. ولا يُعلَن غيابُ مصدرٍ حاكم قبل البحث في الخريطة كلها</t>
         </is>
       </c>
       <c r="C18" s="2" t="n"/>
@@ -962,12 +963,12 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>م 107</t>
+          <t>م 113</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>الفرق بين تشغيل المصالحة وإغلاقها حاكم: تُشغَّل بالاستثناءات المعلنة، ولا يصدر أساس معتمد وفيه مالك مجهول</t>
+          <t>بوابة G0 تمنع بناء وظيفةٍ أو معاملةٍ جديدة ولا تمنع مصالحة معمارية: فتصحيح المالك أو الاسم المعروض أو المجموعة أو الترتيب، وتسجيل سطحٍ قائم، ونقل رابطٍ في الملاحة، وربط معرّف الشاشة — كلها خارج المنع ما لم تمسّ الحبّة أو المعاملة أو آلة الحالة أو مسار الكتابة أو منطق الاعتماد. ولا يُفتح لها استثناء لأنها ليست داخل نطاق المنع أصلًا</t>
         </is>
       </c>
       <c r="C19" s="2" t="n"/>
@@ -978,12 +979,12 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>م 108</t>
+          <t>م 114</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>لا تُلتقط لقطة القياس والبناء جارٍ: إمّا تُجمَّد اللقطة ثم يجري البناء ويُعاد القياس، أو يُجمَّد البناء في نافذة القياس</t>
+          <t>الإدارة تملك العملية · والدور يحدد من ينفّذها · والنطاق (موقع أو مخزن أو مشروع) يحدد أي السجلات يبلغها · والشاشة واحدة مشتركة تُصفّى بالنطاق — ولا تُنسخ شاشة لكل صاحب نطاق ولا يُرفع اسم دورٍ إلى مرتبة إدارة</t>
         </is>
       </c>
       <c r="C20" s="2" t="n"/>
@@ -994,12 +995,12 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>م 109</t>
+          <t>م 111</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>لا يُعرض للمستخدم اسم غير معتمد — والاسم المعروض بلا اعتماد عيب حوكمة لا تفصيل تسمية؛ وتمنع البوابة دخول أي متغيّر برمجي أو رمز تقني أو اسم ملف أو جدول إلى الاسم المعياري ويُختبر الحارس سلبيًّا</t>
+          <t>الصفر المقيس يُكتب صفرًا ولا يُترك فراغًا: الفراغ يعني «غير مقيس» والصفر يعني «قيس فكان صفرًا» — وكل أداة توليد تُفحص بأن تُخرِج صفرًا واحدًا مقيسًا وتُقرأ صفرًا لا خانةً خالية</t>
         </is>
       </c>
       <c r="C21" s="2" t="n"/>
@@ -1010,12 +1011,12 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>م 110</t>
+          <t>م 112</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>لا يحقّق أحد في نفسه ولا فيمن يديره ولا فيمن يديره هو: السلوك الوظيفي للموارد · والنزاهة وكسر الضابط للحوكمة · والمراجعة الداخلية بتكليف مكتوب لكل حالة بلا اختصاص أصيل — والتصعيد بتعارض المصلحة بالحالة لا بملكية السياسة</t>
+          <t>كل حقل في سجل الحقول يحمل مصدره: الجدول أو الكيان الذي جاء منه إلى جانب اسمه التقني — وبلا مفتاح المصدر لا تُربط سياسة على مستوى الحقل (حساسية · تقنيع · صلاحية) إلا بالاسم وحده وهو يُفرِط في الوسم عبر الشاشات</t>
         </is>
       </c>
       <c r="C22" s="2" t="n"/>
@@ -1026,12 +1027,12 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>م 2 · 90</t>
+          <t>م 101</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>لكل حقيقة مالك واحد ومستهلكون بلا حد — ولا نسخ يدوية: FK/Reference لا تكرار الاسم في سبعة جداول</t>
+          <t>كل سطح يُسجَّل مصدرَ حقيقة يحمل صراحةً أربعًا: الحبّة · والإدارة المالكة · والكيان المعياري · والمعرّف المعياري — وبوابة تكشف سطحين مصدرَي حقيقة لكيان وحبّة واحدة وتمنع إنشاء حالة جديدة</t>
         </is>
       </c>
       <c r="C23" s="2" t="n"/>
@@ -1042,12 +1043,12 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>م 7 · 5</t>
+          <t>م 102</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Grain ذري: إن احتمل التعريف «واحد أو أكثر» فالتصميم مرفوض — وكل 1:N في Child Register</t>
+          <t>التقرير الذي يجمع أكثر من إدارة لا يملك الحقائق التي يجمعها — يُصنَّف إسقاطًا مؤسسيًّا مشتركًا وتبقى كل حقيقة عند مالكها ولا يُجبَر على مالك واحد منها</t>
         </is>
       </c>
       <c r="C24" s="2" t="n"/>
@@ -1058,12 +1059,12 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>م 8 · 83</t>
+          <t>م 103</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>كل دورة State Machine: حالات وانتقالات مسموحة وممنوعة ومن يملكها وشروطها وأثرها — ولا Status حر</t>
+          <t>السطح الذي تحتاجه كل الإدارات يُبنى إسقاطًا موحّدًا معلَّمًا بنطاق الإدارة والدور والمشروع — لا نسخة لكل إدارة</t>
         </is>
       </c>
       <c r="C25" s="2" t="n"/>
@@ -1074,12 +1075,12 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>م 9 · 10 · 53</t>
+          <t>م 104</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>كل زر إنشاء بوابة أعمال — والقاعدة الحرجة في Service/Domain Layer لا في الواجهة، والاختبار السالب إلزامي</t>
+          <t>لا يُدمج سطح تبويبًا إلا بإثبات الأب المعياري وحبّة الابن ونوع العلاقة ودورة حياته وصلاحيته المستقلة ورابطه العميق وحاجته للوصول المباشر — ولا تُضحّى الصلاحية لأجل ترتيب أجمل للسايدبار</t>
         </is>
       </c>
       <c r="C26" s="2" t="n"/>
@@ -1090,12 +1091,12 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>م 11</t>
+          <t>م 105</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>سجل رفض موحد: من حاول تجاوز ماذا ومتى وكم مرة</t>
+          <t>معيار إغلاق النقص تغطية المؤهَّل لا العدد: مكوّن مركزي واحد يُستدعى في الأسطح المؤهَّلة، ولا يُوضع على استمارة فردية ولا لوحة ولا إعداد ثابت لبلوغ رقم</t>
         </is>
       </c>
       <c r="C27" s="2" t="n"/>
@@ -1106,12 +1107,12 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>م 12 · 49</t>
+          <t>م 106</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>التكامل ثلاثة أنواع لا تختلط: Reference · Event Effect · Command/Request — ولا أثر خارج مصفوفة التكامل</t>
+          <t>يمنع تشغيل المصالحة ثلاثة: تكرار مصدر الحقيقة · وسطح يكتب ومالك حقيقته مجهول · ومسار كتابة يعبر حدود إدارة بلا عقد معتمد — ولا يمنعها السطح القارئ اليتيم؛ يُعلَن استثناءً ويُستثنى من المقام المغلق</t>
         </is>
       </c>
       <c r="C28" s="2" t="n"/>
@@ -1122,12 +1123,12 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>م 16 · 85 · 86</t>
+          <t>م 107</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>لا تعديل مباشر لحقيقة إدارة أخرى: حدث ← Gate عند المالك · التصحيح يُنشر Correction Event · والإلغاء بتعويض لا حذف</t>
+          <t>الفرق بين تشغيل المصالحة وإغلاقها حاكم: تُشغَّل بالاستثناءات المعلنة، ولا يصدر أساس معتمد وفيه مالك مجهول</t>
         </is>
       </c>
       <c r="C29" s="2" t="n"/>
@@ -1138,12 +1139,12 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>م 17 · 39</t>
+          <t>م 108</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>الاعتماد محرك واحد (AAM) بمحدداته — ولا Hardcode لاسم أو منصب: Role_Key/Approval_Rule_ID يُحل وقت التنفيذ</t>
+          <t>لا تُلتقط لقطة القياس والبناء جارٍ: إمّا تُجمَّد اللقطة ثم يجري البناء ويُعاد القياس، أو يُجمَّد البناء في نافذة القياس</t>
         </is>
       </c>
       <c r="C30" s="2" t="n"/>
@@ -1154,12 +1155,12 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>م 18 · 19 · 21</t>
+          <t>م 109</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>منع التجزئة بمفتاح ونافذة · الميزانية ≠ الالتزام ≠ الدفع ≠ التنفيذ · والاستحقاق ≠ السداد والتخصيص كيان</t>
+          <t>لا يُعرض للمستخدم اسم غير معتمد — والاسم المعروض بلا اعتماد عيب حوكمة لا تفصيل تسمية؛ وتمنع البوابة دخول أي متغيّر برمجي أو رمز تقني أو اسم ملف أو جدول إلى الاسم المعياري ويُختبر الحارس سلبيًّا</t>
         </is>
       </c>
       <c r="C31" s="2" t="n"/>
@@ -1170,12 +1171,12 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>م 20</t>
+          <t>م 110</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>المالية تملك الاعتراف والقيد والذمم والإقفال وGL — والخزينة الحسابات والقبض والصرف والتنفيذ؛ وغيرهما يطلب ويرى الحالة</t>
+          <t>لا يحقّق أحد في نفسه ولا فيمن يديره ولا فيمن يديره هو: السلوك الوظيفي للموارد · والنزاهة وكسر الضابط للحوكمة · والمراجعة الداخلية بتكليف مكتوب لكل حالة بلا اختصاص أصيل — والتصعيد بتعارض المصلحة بالحالة لا بملكية السياسة</t>
         </is>
       </c>
       <c r="C32" s="2" t="n"/>
@@ -1186,12 +1187,12 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>م 23 · 24 · 25</t>
+          <t>م 2 · 90</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>الإقفال كيان بأنواعه لا Status · Current State ≠ History · ولا overwrite بعد الاعتماد (Version/Amendment/Reversal)</t>
+          <t>لكل حقيقة مالك واحد ومستهلكون بلا حد — ولا نسخ يدوية: FK/Reference لا تكرار الاسم في سبعة جداول</t>
         </is>
       </c>
       <c r="C33" s="2" t="n"/>
@@ -1202,12 +1203,12 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>م 26 · 27 · 84</t>
+          <t>م 7 · 5</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Document Control Model موحد — والدليل Document_ID لا مسار ملف؛ ولا إجراء بلا سياق مستندي حيث يلزم</t>
+          <t>Grain ذري: إن احتمل التعريف «واحد أو أكثر» فالتصميم مرفوض — وكل 1:N في Child Register</t>
         </is>
       </c>
       <c r="C34" s="2" t="n"/>
@@ -1218,12 +1219,12 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>م 32 · 42 · 72 · 73</t>
+          <t>م 8 · 83</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>كل مشتقة صفر إدخال أعمال — والتقارير تُبنى من المصادر ولا تُدخل مرتين، وكل رقم قابل للنزول حتى الحقيقة</t>
+          <t>كل دورة State Machine: حالات وانتقالات مسموحة وممنوعة ومن يملكها وشروطها وأثرها — ولا Status حر</t>
         </is>
       </c>
       <c r="C35" s="2" t="n"/>
@@ -1234,12 +1235,12 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>م 37 · 38 · 81 · 82</t>
+          <t>م 9 · 10 · 53</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Canonical Lookup Registry · Derivation Dictionary · KPI Catalog · SLA Catalog — لكل قيمة بيتٌ واحد وقاعدة معلنة</t>
+          <t>كل زر إنشاء بوابة أعمال — والقاعدة الحرجة في Service/Domain Layer لا في الواجهة، والاختبار السالب إلزامي</t>
         </is>
       </c>
       <c r="C36" s="2" t="n"/>
@@ -1250,12 +1251,12 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>م 45 · 47 · 48 · 88</t>
+          <t>م 11</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>كل أثر مالي Idempotent · ولا تكامل صامت: Pending/Processed/Failed/Retrying/Dead Letter/Compensated بمراقبة معلنة</t>
+          <t>سجل رفض موحد: من حاول تجاوز ماذا ومتى وكم مرة</t>
         </is>
       </c>
       <c r="C37" s="2" t="n"/>
@@ -1266,12 +1267,12 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>م 74 · 75 · 76</t>
+          <t>م 12 · 49</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>الأمن على مستوى الحقل حيث يلزم · الأثر الحساس Append-Only · وكل حدث حاكم: من وبصفة من وعن من ومتى وأين</t>
+          <t>التكامل ثلاثة أنواع لا تختلط: Reference · Event Effect · Command/Request — ولا أثر خارج مصفوفة التكامل</t>
         </is>
       </c>
       <c r="C38" s="2" t="n"/>
@@ -1282,12 +1283,12 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>م 78 · 79 · 80</t>
+          <t>م 16 · 85 · 86</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>لكل قاعدة Valid_From/To وVersion — ويُطبَّق ما كان نافذًا لحظة الحدث لا ما استُحدث بعده</t>
+          <t>لا تعديل مباشر لحقيقة إدارة أخرى: حدث ← Gate عند المالك · التصحيح يُنشر Correction Event · والإلغاء بتعويض لا حذف</t>
         </is>
       </c>
       <c r="C39" s="2" t="n"/>
@@ -1298,12 +1299,12 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>م 54 · 56 · 95</t>
+          <t>م 17 · 39</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>الإغلاق خمس مراحل ولا يُختصر — وتُعرض النسب منفصلة: بنيوي · تكامل · بيانات · اختبار · قبول</t>
+          <t>الاعتماد محرك واحد (AAM) بمحدداته — ولا Hardcode لاسم أو منصب: Role_Key/Approval_Rule_ID يُحل وقت التنفيذ</t>
         </is>
       </c>
       <c r="C40" s="2" t="n"/>
@@ -1311,24 +1312,190 @@
       <c r="E40" s="2" t="n"/>
       <c r="F40" s="3" t="n"/>
     </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>م 18 · 19 · 21</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>منع التجزئة بمفتاح ونافذة · الميزانية ≠ الالتزام ≠ الدفع ≠ التنفيذ · والاستحقاق ≠ السداد والتخصيص كيان</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>م 20</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>المالية تملك الاعتراف والقيد والذمم والإقفال وGL — والخزينة الحسابات والقبض والصرف والتنفيذ؛ وغيرهما يطلب ويرى الحالة</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n"/>
+      <c r="E42" s="2" t="n"/>
+      <c r="F42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>م 23 · 24 · 25</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>الإقفال كيان بأنواعه لا Status · Current State ≠ History · ولا overwrite بعد الاعتماد (Version/Amendment/Reversal)</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="n"/>
+      <c r="F43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>م 26 · 27 · 84</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Document Control Model موحد — والدليل Document_ID لا مسار ملف؛ ولا إجراء بلا سياق مستندي حيث يلزم</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>م 32 · 42 · 72 · 73</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>كل مشتقة صفر إدخال أعمال — والتقارير تُبنى من المصادر ولا تُدخل مرتين، وكل رقم قابل للنزول حتى الحقيقة</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>م 37 · 38 · 81 · 82</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Canonical Lookup Registry · Derivation Dictionary · KPI Catalog · SLA Catalog — لكل قيمة بيتٌ واحد وقاعدة معلنة</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="n"/>
+      <c r="F46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>م 45 · 47 · 48 · 88</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>كل أثر مالي Idempotent · ولا تكامل صامت: Pending/Processed/Failed/Retrying/Dead Letter/Compensated بمراقبة معلنة</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="n"/>
+      <c r="F47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>م 74 · 75 · 76</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>الأمن على مستوى الحقل حيث يلزم · الأثر الحساس Append-Only · وكل حدث حاكم: من وبصفة من وعن من ومتى وأين</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" s="2" t="n"/>
+      <c r="F48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>م 78 · 79 · 80</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>لكل قاعدة Valid_From/To وVersion — ويُطبَّق ما كان نافذًا لحظة الحدث لا ما استُحدث بعده</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>م 54 · 56 · 95</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>الإغلاق خمس مراحل ولا يُختصر — وتُعرض النسب منفصلة: بنيوي · تكامل · بيانات · اختبار · قبول</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="3" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="44">
+    <mergeCell ref="B47:F47"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B46:F46"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B48:F48"/>
     <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B42:F42"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B44:F44"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="B38:F38"/>
@@ -1337,16 +1504,391 @@
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B49:F49"/>
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B45:F45"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B50:F50"/>
     <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B41:F41"/>
     <mergeCell ref="B35:F35"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>خريطة المصادر الحاكمة — لكل كونٍ مصدرُه (م 122)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="3" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>لا يُعلَن غيابُ مصدرٍ حاكم لأي نطاق قبل البحث في هذه الخريطة كلها · ولا يُشتقّ هدفٌ من الوضع القائم حيث يوجد مصدرٌ هنا (م 115)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>الرمز</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>النطاق</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>المصدر الحاكم</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>تصنيف المصدر</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>ما يُستخرج منه</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>DEP-01..17</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>الإدارات السبع عشرة</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>الملف ٠١ — الدليل المعماري الموحد · ورقةٌ لكل إدارة</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>حاكم</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>الأسطح والمجموعات والترتيب والحبّة والحقول والملكية</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>EX-CEO</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>مساحة الرئيس التنفيذي</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>الملف ٠٢ — القيادة · ورقة الرئيس</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>حاكم</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>ستة وعشرون سطحًا بمجموعاتها ومصفوفة سلطة الاعتماد</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>EX-DVP</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>مساحة نواب الرئيس</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>الملف ٠٢ — القيادة · ورقة النواب</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>حاكم</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>اثنا عشر سطحًا بمحرك النطاق والإنابة</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>WS-MY</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>مساحة عملي</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>الملف ٠١ — ورقة مساحة عملي</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>حاكم</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>الأسطح الشخصية — إسقاطٌ ومُطلِق طلبات لا مصدر حقيقة</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>IAF</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>المراجعة الداخلية المستقلة</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>الملف ٠١ — ورقة المراجعة الداخلية</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>حاكم</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>سبعة عشر سطحًا بميثاقها وكونها الرقابي</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>PLATFORM</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>القدرات المنصّية المشتركة</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>أحكام المنصّة بمعاييرها الأربعة</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>حاكم</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>ما استوفى الأربعة: ثلاث إدارات فأكثر · بلا حقيقة أعمال · بمالكٍ تقنيّ · مسجَّل</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>المتطلبات وآلات الحالة والأحداث</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>الملفات ٠٤–٠٨ — الموجات الخمس</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>حاكم</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>المتطلبات الذرية وفصل الواجبات وعقود الأثر والسيناريوهات</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>القرارات</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>الملف ٠٩ — سجل القرارات الحاكم</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>حاكم</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>كل قرارٍ معتمد أو مفتوح بحالته ودرجة حجبه</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>المبادئ والقواعد</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>الملف ٠٣ — الدستور</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>حاكم</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>المواد المئة والاثنتان والعشرون</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>واقع النظام المبنيّ</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>سجل الشاشات ولقطات القياس</t>
+        </is>
+      </c>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>مرجعٌ يُقاس عليه</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="inlineStr">
+        <is>
+          <t>حالةٌ راهنة — تقترح كشفًا ولا تعتمد نفسها هدفًا (م 115)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>هذه الخريطة نفسها</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="inlineStr">
+        <is>
+          <t>الملف ٠٣ — هذا الشيت</t>
+        </is>
+      </c>
+      <c r="D15" s="28" t="inlineStr">
+        <is>
+          <t>مرجع</t>
+        </is>
+      </c>
+      <c r="E15" s="28" t="inlineStr">
+        <is>
+          <t>لا تُقرأ في زمن التشغيل فلا تُعدّ سجلًّا حاكمًا (م 116)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1485,7 +2027,7 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>98 شاشة · 1999 حقلًا</t>
+          <t>99 شاشة · 2016 حقلًا</t>
         </is>
       </c>
     </row>
@@ -1549,7 +2091,7 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>82 شاشة · 1231 حقلًا — لا تشمل HSE</t>
+          <t>82 شاشة · 1235 حقلًا — لا تشمل HSE</t>
         </is>
       </c>
     </row>
@@ -2629,7 +3171,7 @@
         <v>4</v>
       </c>
       <c r="I12" s="16" t="n">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -3130,19 +3672,19 @@
         </is>
       </c>
       <c r="E21" s="16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F21" s="16" t="n">
         <v>3</v>
       </c>
       <c r="G21" s="16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H21" s="16" t="n">
         <v>3</v>
       </c>
       <c r="I21" s="16" t="n">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -3297,13 +3839,13 @@
       </c>
       <c r="D24" s="17" t="inlineStr"/>
       <c r="E24" s="17" t="n">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F24" s="17" t="inlineStr"/>
       <c r="G24" s="17" t="inlineStr"/>
       <c r="H24" s="17" t="inlineStr"/>
       <c r="I24" s="17" t="n">
-        <v>6910</v>
+        <v>6931</v>
       </c>
       <c r="J24" s="17" t="inlineStr"/>
       <c r="K24" s="17" t="inlineStr"/>
@@ -23363,7 +23905,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>النطاق المقيس: 6910 حقلًا في 395 شاشة بالدليل + 677 حقلًا في 38 شاشة بالقيادة = 7587 حقلًا يلزم لكلٍّ منها سطر تتبع بثمانية عشر عمودًا</t>
+          <t>النطاق المقيس: 6931 حقلًا في 396 شاشة بالدليل + 677 حقلًا في 38 شاشة بالقيادة = 7608 حقلًا يلزم لكلٍّ منها سطر تتبع بثمانية عشر عمودًا</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
